--- a/medical_surveys_questionnaires/043_male_medical_questionnaire--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/043_male_medical_questionnaire--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>patient_demographics</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>patient_contact_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_social_history</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>medical_social_history</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>male_medical_questionnaire_second_page</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Male Medical Questionnaire second page</t>
+          <t>Allergies</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medication_allergies</t>
+          <t>family_medical_history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medication_allergies</t>
+          <t>Family Medical History</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_social_history_additional</t>
+          <t>mental_health_issues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_social_history_additional</t>
+          <t>Mental Health Issues</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>male_medical_questionnaire_third_page</t>
+          <t>mental_health_treatment_history</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Male Medical Questionnaire third page</t>
+          <t>Mental Health Treatment History</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_surgical_history</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_surgical_history</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_medical_history_additional</t>
+          <t>surgical_history</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medical_medical_history_additional</t>
+          <t>Surgical History</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>male_medical_questionnaire_fourth_page</t>
+          <t>medical_insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Male Medical Questionnaire fourth page</t>
+          <t>Medical Insurance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>family_medical_history</t>
+          <t>active_medical_conditions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>family_medical_history</t>
+          <t>Active Medical Conditions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_social_history_additional</t>
+          <t>male_medical_questionnaire_second_page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical_social_history_additional</t>
+          <t>Male Medical Questionnaire second page</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>male_medical_questionnaire_fifth_page</t>
+          <t>male_medical_questionnaire_third_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Male Medical Questionnaire fifth page</t>
+          <t>Male Medical Questionnaire third page</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_medical_social_history</t>
+          <t>male_medical_questionnaire_fourth_page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>medical_medical_social_history</t>
+          <t>Male Medical Questionnaire fourth page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_medical_social_history_additional</t>
+          <t>male_medical_questionnaire_fifth_page</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medical_medical_social_history_additional</t>
+          <t>Male Medical Questionnaire fifth page</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medical_mental_health_history</t>
+          <t>male_medical_questionnaire_seventh_page</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>medical_mental_health_history</t>
+          <t>Male Medical Questionnaire seventh page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medical_medical_mental_health_history_additional</t>
+          <t>male_medical_questionnaire_eighth_page</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>medical_mental_health_history_additional</t>
+          <t>Male Medical Questionnaire eighth page</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>male_medical_questionnaire_seventh_page</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Male Medical Questionnaire seventh page</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_medical_mental_health_history</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>medical_mental_health_history</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>medical_medical_mental_health_history_additional</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>medical_mental_health_history_additional</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>male_medical_questionnaire_eighth_page</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Male Medical Questionnaire eighth page</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_medical_mental_health_history_additional</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>medical_mental_health_history_additional</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>male_medical_questionnaire_ninth_page</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Male Medical Questionnaire ninth page</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +963,9 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +988,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>allergies_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'name':_'allergy-1',_'label':_'allergy_1'}</t>
+          <t>allergy_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'name': 'allergy-1', 'label': 'Allergy 1'}</t>
+          <t>Allergy 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>allergies_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'name':_'allergy-2',_'label':_'allergy_2'}</t>
+          <t>allergy_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'name': 'allergy-2', 'label': 'Allergy 2'}</t>
+          <t>Allergy 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>allergies_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'name':_'allergy-3',_'label':_'allergy_3'}</t>
+          <t>allergy_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'name': 'allergy-3', 'label': 'Allergy 3'}</t>
+          <t>Allergy 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'12-1',_'name':_'family_history_1',_'label':_'family_history_1'}</t>
+          <t>family_history_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '12-1', 'name': 'family_history_1', 'label': 'Family History 1'}</t>
+          <t>Family History 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'12-2',_'name':_'family_history_2',_'label':_'family_history_2'}</t>
+          <t>family_history_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '12-2', 'name': 'family_history_2', 'label': 'Family History 2'}</t>
+          <t>Family History 2</t>
         </is>
       </c>
     </row>
@@ -1216,63 +1078,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'12-3',_'name':_'family_history_3',_'label':_'family_history_3'}</t>
+          <t>family_history_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '12-3', 'name': 'family_history_3', 'label': 'Family History 3'}</t>
+          <t>Family History 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medical_mental_health_history_choices</t>
+          <t>mental_health_issues_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'18-1',_'name':_'mental_health_issue_1',_'label':_'mental_health_issue_1'}</t>
+          <t>mental_health_issue_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '18-1', 'name': 'mental_health_issue_1', 'label': 'Mental Health Issue 1'}</t>
+          <t>Mental Health Issue 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medical_mental_health_history_choices</t>
+          <t>mental_health_issues_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'18-2',_'name':_'mental_health_issue_2',_'label':_'mental_health_issue_2'}</t>
+          <t>mental_health_issue_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '18-2', 'name': 'mental_health_issue_2', 'label': 'Mental Health Issue 2'}</t>
+          <t>Mental Health Issue 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_mental_health_history_choices</t>
+          <t>mental_health_issues_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'18-3',_'name':_'mental_health_issue_3',_'label':_'mental_health_issue_3'}</t>
+          <t>mental_health_issue_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '18-3', 'name': 'mental_health_issue_3', 'label': 'Mental Health Issue 3'}</t>
+          <t>Mental Health Issue 3</t>
         </is>
       </c>
     </row>
